--- a/human_validation/judge/kor/judge_D021_S003_P002__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D021_S003_P002__qwen3-235b_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,208 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 것을 환영합니다. 오늘 어떤 일로 오셨는지 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 직장 건강검진에서 이 모든 게 시작됐어요. 거기 의사 선생님이 제 체중이 너무 낮다고 하셔서 오라고 하셨어요. 저는 딱히 아프다거나 그런 느낌은 없어요. 그냥 몸이 가볍고, 농구할 때 더 잘 움직이는 것 같고, 정비소에서 일할 때도 덜 무거운 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 요즘 식욕이나 먹는 양에 변화가 있으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 네, 예전보다 덜 먹는 것 같아요. 대부분 날에는 아침에 커피만 마시고, 나중에 작은 샌드위치나 뭐든 있는 것의 반쯤 먹어요. 정비소가 늦게까지 돌아가고 집도 바쁘다 보니까, 그냥 제 나름의 단순한 루틴을 지키는 게 더 편해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 일부러 체중을 줄이신 건가요, 아니면 의도치 않게 체중이 줄으신 건가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 그러니까, 부분적으로는 일부러인 것 같아요. 대부분 날에는 꽤 가볍게 먹어요. 아침에 커피, 나중에 작은 샌드위치나 뭐든 있는 것의 반쯤이요. 정비소가 늦게까지 돌아가고 집도 바쁘다 보니까, 제 나름의 단순한 규칙을 지키는 게 그냥 더 나은 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 덜 드시는 게 스스로 선택한 건가요, 아니면 음식이 맛이 없거나 금방 배가 부르거나 먹는 것에 흥미를 잃어서 먹기가 더 힘들어지신 건가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 제가 선택하는 쪽에 더 가까운 것 같아요. 음식이 맛없다거나 그런 건 아니고, 그냥 가볍게 먹는 거예요. 대부분 날에는 아침에 커피, 나중에 작은 샌드위치나 뭐든 있는 것의 반쯤이요. 정비소가 늦게까지 돌아가고 집도 바쁘다 보니까, 제 나름의 단순한 규칙을 지키는 게 더 나은 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 체중을 낮게 유지하려고 의도적으로 음식량을 제한하거나 특정 음식을 피하고 계신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 네, 제한하고 있어요. 대부분 날에는 그냥 아침에 커피만 마시고, 나중에 작은 샌드위치나 뭐든 있는 것의 반쯤 먹어요. 정비소가 늦게까지 돌아가고 집도 바쁘다 보니까, 제 나름의 단순한 규칙을 지키면 그냥 더 나은 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 체중을 조절하려고 일부러 몸을 아프게 하거나 변비약이나 이뇨제 같은 약을 사용하신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 아니요, 딱히 없어요. 일부러 아프게 하거나 그런 걸 사용한 적은 없어요. 그냥 음식량을 적게 유지하는 정도예요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 최근에 피로감, 힘이 없는 느낌, 피부나 머리카락, 손톱의 변화 같은 신체 증상을 느끼신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 잘 모르겠어요. 그렇게 큰 건 딱히 못 느꼈어요. 가끔 지치긴 하는데, 그냥 일이랑 이것저것 때문일 거라고 생각해요. 피부나 머리카락, 손톱에는 별로 신경을 안 썼어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 다른 사람들은 정상 체중이거나 오히려 저체중으로 볼 수 있는데도, 체중이 늘거나 뚱뚱해질까 봐 걱정되시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 네... 걱정돼요. 체중계 숫자가 1파운드라도 올라가거나 청바지가 조금이라도 꽉 끼면, 몸이 물러지고 있다는 생각이 들기 시작해요. 그럼 일할 때 차 주변을 움직이거나 코트를 오갈 때 느려질까 봐 걱정돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 거울을 보거나 다른 사람들이 말랐다고 말할 때도, 본인이 과체중이거나 체중을 더 줄여야 한다고 보시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 그러니까... 사람들이 저더러 말랐다고 하고 걱정하는 건 아는데, 저는 그렇게는 안 봐요. 그냥 너무 크게 받아들이는 것 같아요. 저는 여전히 출근하고, 집안일도 처리하고, 주말에 공도 하고 있어서, 그렇게 심각하게 느껴지지 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>진단명: 신경성 식욕부진증 (D021)
 인구통계: 성별 남성 / 나이 44 / 직업상태 automotive service technician or mechanic / 최종학력 고등학교 졸업
@@ -575,257 +768,35 @@
 증상 지속 기간: None
 추가 요건: 
 주호소 증상 코드: S044
-배경 서술: 연로한 친척이 들어와 살게 되면서 스티븐의 집안 상황이 바뀌었고, 부엌과 가족 일정은 늦은 정비소 근무, 머스탱 프로젝트, 주말 지역사회 활동 위에 돌봄 루틴으로 채워지게 되었다. 그는 이에 대응해 자신의 식사를 엄격하고 스스로 부과한 체계로 조여갔는데, 본인 말로는 농구를 위해 몸을 가볍게 유지하고 스트레스받는 한 주 동안 절제를 지키기 위한 것이었다. 이 패턴은 점차 그의 체중을 건강한 수준보다 낮게 만들었다. 체중 감소는 임상적으로 상당한 수준이었지만, 그는 이를 실용적인 조정 정도로 축소해 생각했고, 체중을 다시 늘리는 것에 강하게 반대하며 체중이 늘면 몸이 둔해질 거라고 주장했다. 직장을 위한 정기 건강검진에서 저체중이 기록된 후 1차 진료의를 통해 진료를 받게 되었고, 스티븐은 주로 계속 일하고 리그에서 뛸 수 있는 능력을 지키기 위해 정신과 의뢰에 동의했다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 것을 환영합니다. 오늘 어떤 일로 오셨는지 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 직장 건강검진에서 이 모든 게 시작됐어요. 거기 의사 선생님이 제 체중이 너무 낮다고 하셔서 오라고 하셨어요. 저는 딱히 아프다거나 그런 느낌은 없어요. 그냥 몸이 가볍고, 농구할 때 더 잘 움직이는 것 같고, 정비소에서 일할 때도 덜 무거운 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 요즘 식욕이나 먹는 양에 변화가 있으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 네, 예전보다 덜 먹는 것 같아요. 대부분 날에는 아침에 커피만 마시고, 나중에 작은 샌드위치나 뭐든 있는 것의 반쯤 먹어요. 정비소가 늦게까지 돌아가고 집도 바쁘다 보니까, 그냥 제 나름의 단순한 루틴을 지키는 게 더 편해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 일부러 체중을 줄이신 건가요, 아니면 의도치 않게 체중이 줄으신 건가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 그러니까, 부분적으로는 일부러인 것 같아요. 대부분 날에는 꽤 가볍게 먹어요. 아침에 커피, 나중에 작은 샌드위치나 뭐든 있는 것의 반쯤이요. 정비소가 늦게까지 돌아가고 집도 바쁘다 보니까, 제 나름의 단순한 규칙을 지키는 게 그냥 더 나은 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 덜 드시는 게 스스로 선택한 건가요, 아니면 음식이 맛이 없거나 금방 배가 부르거나 먹는 것에 흥미를 잃어서 먹기가 더 힘들어지신 건가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 제가 선택하는 쪽에 더 가까운 것 같아요. 음식이 맛없다거나 그런 건 아니고, 그냥 가볍게 먹는 거예요. 대부분 날에는 아침에 커피, 나중에 작은 샌드위치나 뭐든 있는 것의 반쯤이요. 정비소가 늦게까지 돌아가고 집도 바쁘다 보니까, 제 나름의 단순한 규칙을 지키는 게 더 나은 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 체중을 낮게 유지하려고 의도적으로 음식량을 제한하거나 특정 음식을 피하고 계신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 네, 제한하고 있어요. 대부분 날에는 그냥 아침에 커피만 마시고, 나중에 작은 샌드위치나 뭐든 있는 것의 반쯤 먹어요. 정비소가 늦게까지 돌아가고 집도 바쁘다 보니까, 제 나름의 단순한 규칙을 지키면 그냥 더 나은 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 체중을 조절하려고 일부러 몸을 아프게 하거나 변비약이나 이뇨제 같은 약을 사용하신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 아니요, 딱히 없어요. 일부러 아프게 하거나 그런 걸 사용한 적은 없어요. 그냥 음식량을 적게 유지하는 정도예요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 최근에 피로감, 힘이 없는 느낌, 피부나 머리카락, 손톱의 변화 같은 신체 증상을 느끼신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 잘 모르겠어요. 그렇게 큰 건 딱히 못 느꼈어요. 가끔 지치긴 하는데, 그냥 일이랑 이것저것 때문일 거라고 생각해요. 피부나 머리카락, 손톱에는 별로 신경을 안 썼어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 다른 사람들은 정상 체중이거나 오히려 저체중으로 볼 수 있는데도, 체중이 늘거나 뚱뚱해질까 봐 걱정되시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 네... 걱정돼요. 체중계 숫자가 1파운드라도 올라가거나 청바지가 조금이라도 꽉 끼면, 몸이 물러지고 있다는 생각이 들기 시작해요. 그럼 일할 때 차 주변을 움직이거나 코트를 오갈 때 느려질까 봐 걱정돼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 거울을 보거나 다른 사람들이 말랐다고 말할 때도, 본인이 과체중이거나 체중을 더 줄여야 한다고 보시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 그러니까... 사람들이 저더러 말랐다고 하고 걱정하는 건 아는데, 저는 그렇게는 안 봐요. 그냥 너무 크게 받아들이는 것 같아요. 저는 여전히 출근하고, 집안일도 처리하고, 주말에 공도 하고 있어서, 그렇게 심각하게 느껴지지 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
+배경 서술: 연로한 친척이 들어와 살게 되면서 스티븐의 집안 상황이 바뀌었고, 부엌과 가족 일정은 늦은 정비소 근무, 머스탱 프로젝트, 주말 지역사회 활동 위에 돌봄 루틴으로 채워지게 되었다. 그는 이에 대응해 자신의 식사를 엄격하고 스스로 부과한 체계로 조여갔는데, 본인 말로는 농구를 위해 몸을 가볍게 유지하고 스트레스받는 한 주 동안 절제를 지키기 위한 것이었다. 이 패턴은 점차 그의 체중을 건강한 수준보다 낮게 만들었다. 체중 감소는 임상적으로 상당한 수준이었지만, 그는 이를 실용적인 조정 정도로 축소해 생각했고, 체중을 다시 늘리는 것에 강하게 반대하며 체중이 늘면 몸이 둔해질 거라고 주장했다. 직장을 위한 정기 건강검진에서 저체중이 기록된 후 1차 진료의를 통해 진료를 받게 되었고, 스티븐은 주로 계속 일하고 리그에서 뛸 수 있는 능력을 지키기 위해 정신과 의뢰에 동의했다.
+표집된 증상 목록:
+  - S043 섭취 제한: 필요량에 비해 에너지 섭취를 지속적으로 제한하여 체중이 현저히 낮아짐.
+  - S044 저체중: 나이, 성별, 발달 궤적, 신체 건강에 비추어 최소한의 건강 수준보다 현저히 낮은 체중.
+  - S045 체중 증가에 대한 두려움: 현저히 낮은 체중임에도 체중이 늘거나 살이 찌는 것에 대한 강한 두려움.
+  - S084 저체중 심각성 미인식: 현재의 저체중 상태가 심각하다는 것을 지속적으로 인식하지 못함.</t>
+        </is>
+      </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>[9번째 턴 · 의사의 감별진단] 고확률: 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 신경성 식욕부진증 (D021, ICD: F50.0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: anorexia_nervosa (관계=must_include, 요구개수=4, 충족개수=4, 커버리지=1.0)
-  확인된 근거: 섭취 제한: 필요량에 비해 에너지 섭취를 지속적으로 제한하여 체중이 현저히 낮아짐.; 저체중: 나이, 성별, 발달 궤적, 신체 건강에 비추어 최소한의 건강 수준보다 현저히 낮은 체중.; 체중 증가에 대한 두려움: 현저히 낮은 체중임에도 체중이 늘거나 살이 찌는 것에 대한 강한 두려움.; 저체중 심각성 미인식: 현재의 저체중 상태가 심각하다는 것을 지속적으로 인식하지 못함.
-  누락: 체형/체중 이미지 왜곡: 체중이나 체형이 자기평가에 지나친 영향을 미침.</t>
+          <t>의사의 최종 진단: 신경성 식욕부진증 (D021, ICD: F50.0)
+지속 기간 요건: None
+기능적 손상 요건: None
+추가 요건: None
+체크리스트 그룹: anorexia_nervosa (관계=must_include, 요구개수=4, 충족개수=4, 커버리지=1.0)
+확인된 근거:
+  - 섭취 제한: 필요량에 비해 에너지 섭취를 지속적으로 제한하여 체중이 현저히 낮아짐.
+  - 저체중: 나이, 성별, 발달 궤적, 신체 건강에 비추어 최소한의 건강 수준보다 현저히 낮은 체중.
+  - 체중 증가에 대한 두려움: 현저히 낮은 체중임에도 체중이 늘거나 살이 찌는 것에 대한 강한 두려움.
+  - 저체중 심각성 미인식: 현재의 저체중 상태가 심각하다는 것을 지속적으로 인식하지 못함.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A43:B43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D021_S003_P002__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D021_S003_P002__qwen3-235b_kor.xlsx
@@ -754,6 +754,11 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -792,11 +797,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A43:B43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D021_S003_P002__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D021_S003_P002__qwen3-235b_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
